--- a/output/topology_excel/9945.xlsx
+++ b/output/topology_excel/9945.xlsx
@@ -425,58 +425,38 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>房间1</t>
+          <t>RoomA</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>类型1</t>
+          <t>RoomB</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>面积1</t>
+          <t>ConnectionType</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>房间2</t>
+          <t>Count</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>类型2</t>
+          <t>Length</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>面积2</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>连接类型</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>数量</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>length</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>width</t>
+          <t>Width</t>
         </is>
       </c>
     </row>
@@ -484,37 +464,21 @@
       <c r="A2" t="n">
         <v>2</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>88277</v>
+      <c r="B2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E2" t="n">
+        <v>126</v>
       </c>
       <c r="F2" t="n">
-        <v>89490</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>门</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I2" t="n">
-        <v>126</v>
-      </c>
-      <c r="J2" t="n">
         <v>13</v>
       </c>
     </row>
@@ -522,37 +486,21 @@
       <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>88277</v>
+      <c r="B3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Hallway</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>90</v>
       </c>
       <c r="F3" t="n">
-        <v>71838</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>门</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I3" t="n">
-        <v>90</v>
-      </c>
-      <c r="J3" t="n">
         <v>13</v>
       </c>
     </row>
@@ -560,37 +508,21 @@
       <c r="A4" t="n">
         <v>1</v>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Living Room</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>200701</v>
+      <c r="B4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Hallway</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>92</v>
       </c>
       <c r="F4" t="n">
-        <v>71838</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>门</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" t="n">
-        <v>92</v>
-      </c>
-      <c r="J4" t="n">
         <v>11</v>
       </c>
     </row>
@@ -598,37 +530,21 @@
       <c r="A5" t="n">
         <v>1</v>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Living Room</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>200701</v>
+      <c r="B5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Kitchen</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>240</v>
       </c>
       <c r="F5" t="n">
-        <v>134176</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>门</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I5" t="n">
-        <v>240</v>
-      </c>
-      <c r="J5" t="n">
         <v>13</v>
       </c>
     </row>
@@ -636,37 +552,21 @@
       <c r="A6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>32136</v>
+      <c r="B6" t="n">
+        <v>8</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
       </c>
       <c r="D6" t="n">
-        <v>8</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>72</v>
       </c>
       <c r="F6" t="n">
-        <v>65913</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>门</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" t="n">
-        <v>72</v>
-      </c>
-      <c r="J6" t="n">
         <v>15</v>
       </c>
     </row>
@@ -674,37 +574,21 @@
       <c r="A7" t="n">
         <v>4</v>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Hallway</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>71838</v>
+      <c r="B7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
       </c>
       <c r="D7" t="n">
-        <v>6</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Kitchen</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E7" t="n">
+        <v>81</v>
       </c>
       <c r="F7" t="n">
-        <v>134176</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>门</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I7" t="n">
-        <v>81</v>
-      </c>
-      <c r="J7" t="n">
         <v>13</v>
       </c>
     </row>
@@ -712,37 +596,21 @@
       <c r="A8" t="n">
         <v>4</v>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Hallway</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>71838</v>
+      <c r="B8" t="n">
+        <v>7</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
       </c>
       <c r="D8" t="n">
-        <v>7</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Hallway</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E8" t="n">
+        <v>90</v>
       </c>
       <c r="F8" t="n">
-        <v>20760</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>门</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" t="n">
-        <v>90</v>
-      </c>
-      <c r="J8" t="n">
         <v>13</v>
       </c>
     </row>
@@ -750,37 +618,21 @@
       <c r="A9" t="n">
         <v>4</v>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Hallway</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>71838</v>
+      <c r="B9" t="n">
+        <v>8</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
       </c>
       <c r="D9" t="n">
-        <v>8</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>80</v>
       </c>
       <c r="F9" t="n">
-        <v>65913</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>门</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>1</v>
-      </c>
-      <c r="I9" t="n">
-        <v>80</v>
-      </c>
-      <c r="J9" t="n">
         <v>13</v>
       </c>
     </row>
@@ -788,37 +640,21 @@
       <c r="A10" t="n">
         <v>1</v>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Living Room</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>200701</v>
+      <c r="B10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>245</v>
       </c>
       <c r="F10" t="n">
-        <v>88277</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>1</v>
-      </c>
-      <c r="I10" t="n">
-        <v>245</v>
-      </c>
-      <c r="J10" t="n">
         <v>11</v>
       </c>
     </row>
@@ -826,37 +662,21 @@
       <c r="A11" t="n">
         <v>1</v>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Living Room</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>200701</v>
+      <c r="B11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
       </c>
       <c r="D11" t="n">
-        <v>4</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Hallway</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E11" t="n">
+        <v>161</v>
       </c>
       <c r="F11" t="n">
-        <v>71838</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>1</v>
-      </c>
-      <c r="I11" t="n">
-        <v>161</v>
-      </c>
-      <c r="J11" t="n">
         <v>11</v>
       </c>
     </row>
@@ -864,37 +684,21 @@
       <c r="A12" t="n">
         <v>1</v>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Living Room</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>200701</v>
+      <c r="B12" t="n">
+        <v>6</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
       </c>
       <c r="D12" t="n">
-        <v>6</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Kitchen</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E12" t="n">
+        <v>479</v>
       </c>
       <c r="F12" t="n">
-        <v>134176</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I12" t="n">
-        <v>479</v>
-      </c>
-      <c r="J12" t="n">
         <v>13</v>
       </c>
     </row>
@@ -902,37 +706,21 @@
       <c r="A13" t="n">
         <v>2</v>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>88277</v>
+      <c r="B13" t="n">
+        <v>3</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E13" t="n">
+        <v>314</v>
       </c>
       <c r="F13" t="n">
-        <v>89490</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>1</v>
-      </c>
-      <c r="I13" t="n">
-        <v>314</v>
-      </c>
-      <c r="J13" t="n">
         <v>13</v>
       </c>
     </row>
@@ -940,37 +728,21 @@
       <c r="A14" t="n">
         <v>2</v>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>88277</v>
+      <c r="B14" t="n">
+        <v>4</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
       </c>
       <c r="D14" t="n">
-        <v>4</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Hallway</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E14" t="n">
+        <v>313</v>
       </c>
       <c r="F14" t="n">
-        <v>71838</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>1</v>
-      </c>
-      <c r="I14" t="n">
-        <v>313</v>
-      </c>
-      <c r="J14" t="n">
         <v>82</v>
       </c>
     </row>
@@ -978,37 +750,21 @@
       <c r="A15" t="n">
         <v>3</v>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>89490</v>
+      <c r="B15" t="n">
+        <v>4</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
       </c>
       <c r="D15" t="n">
-        <v>4</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Hallway</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E15" t="n">
+        <v>58</v>
       </c>
       <c r="F15" t="n">
-        <v>71838</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>1</v>
-      </c>
-      <c r="I15" t="n">
-        <v>58</v>
-      </c>
-      <c r="J15" t="n">
         <v>13</v>
       </c>
     </row>
@@ -1016,37 +772,21 @@
       <c r="A16" t="n">
         <v>3</v>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>89490</v>
+      <c r="B16" t="n">
+        <v>5</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
       </c>
       <c r="D16" t="n">
-        <v>5</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E16" t="n">
+        <v>206</v>
       </c>
       <c r="F16" t="n">
-        <v>32136</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>1</v>
-      </c>
-      <c r="I16" t="n">
-        <v>206</v>
-      </c>
-      <c r="J16" t="n">
         <v>18</v>
       </c>
     </row>
@@ -1054,37 +794,21 @@
       <c r="A17" t="n">
         <v>4</v>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Hallway</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>71838</v>
+      <c r="B17" t="n">
+        <v>5</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
       </c>
       <c r="D17" t="n">
-        <v>5</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E17" t="n">
+        <v>156</v>
       </c>
       <c r="F17" t="n">
-        <v>32136</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
-      <c r="H17" t="n">
-        <v>1</v>
-      </c>
-      <c r="I17" t="n">
-        <v>156</v>
-      </c>
-      <c r="J17" t="n">
         <v>21</v>
       </c>
     </row>
@@ -1092,37 +816,21 @@
       <c r="A18" t="n">
         <v>4</v>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Hallway</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>71838</v>
+      <c r="B18" t="n">
+        <v>6</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Kitchen</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E18" t="n">
+        <v>100</v>
       </c>
       <c r="F18" t="n">
-        <v>134176</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
-      <c r="H18" t="n">
-        <v>1</v>
-      </c>
-      <c r="I18" t="n">
-        <v>100</v>
-      </c>
-      <c r="J18" t="n">
         <v>71</v>
       </c>
     </row>
@@ -1130,37 +838,21 @@
       <c r="A19" t="n">
         <v>4</v>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Hallway</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>71838</v>
+      <c r="B19" t="n">
+        <v>7</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Hallway</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E19" t="n">
+        <v>120</v>
       </c>
       <c r="F19" t="n">
-        <v>20760</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
-      <c r="H19" t="n">
-        <v>1</v>
-      </c>
-      <c r="I19" t="n">
-        <v>120</v>
-      </c>
-      <c r="J19" t="n">
         <v>13</v>
       </c>
     </row>
@@ -1168,37 +860,21 @@
       <c r="A20" t="n">
         <v>4</v>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Hallway</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>71838</v>
+      <c r="B20" t="n">
+        <v>8</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
       </c>
       <c r="D20" t="n">
-        <v>8</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E20" t="n">
+        <v>154</v>
       </c>
       <c r="F20" t="n">
-        <v>65913</v>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
-      <c r="H20" t="n">
-        <v>1</v>
-      </c>
-      <c r="I20" t="n">
-        <v>154</v>
-      </c>
-      <c r="J20" t="n">
         <v>13</v>
       </c>
     </row>
@@ -1206,37 +882,21 @@
       <c r="A21" t="n">
         <v>5</v>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>32136</v>
+      <c r="B21" t="n">
+        <v>8</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E21" t="n">
+        <v>206</v>
       </c>
       <c r="F21" t="n">
-        <v>65913</v>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
-      <c r="H21" t="n">
-        <v>1</v>
-      </c>
-      <c r="I21" t="n">
-        <v>206</v>
-      </c>
-      <c r="J21" t="n">
         <v>15</v>
       </c>
     </row>
@@ -1244,37 +904,21 @@
       <c r="A22" t="n">
         <v>6</v>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Kitchen</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>134176</v>
+      <c r="B22" t="n">
+        <v>7</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
       </c>
       <c r="D22" t="n">
-        <v>7</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Hallway</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E22" t="n">
+        <v>173</v>
       </c>
       <c r="F22" t="n">
-        <v>20760</v>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
-      <c r="H22" t="n">
-        <v>1</v>
-      </c>
-      <c r="I22" t="n">
-        <v>173</v>
-      </c>
-      <c r="J22" t="n">
         <v>8</v>
       </c>
     </row>
@@ -1282,37 +926,21 @@
       <c r="A23" t="n">
         <v>7</v>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Hallway</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>20760</v>
+      <c r="B23" t="n">
+        <v>8</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
       </c>
       <c r="D23" t="n">
-        <v>8</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E23" t="n">
+        <v>173</v>
       </c>
       <c r="F23" t="n">
-        <v>65913</v>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
-      <c r="H23" t="n">
-        <v>1</v>
-      </c>
-      <c r="I23" t="n">
-        <v>173</v>
-      </c>
-      <c r="J23" t="n">
         <v>13</v>
       </c>
     </row>
@@ -1320,37 +948,21 @@
       <c r="A24" t="n">
         <v>8</v>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>65913</v>
+      <c r="B24" t="n">
+        <v>9</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
       </c>
       <c r="D24" t="n">
-        <v>9</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Storage</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E24" t="n">
+        <v>151</v>
       </c>
       <c r="F24" t="n">
-        <v>45451</v>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
-      <c r="H24" t="n">
-        <v>1</v>
-      </c>
-      <c r="I24" t="n">
-        <v>151</v>
-      </c>
-      <c r="J24" t="n">
         <v>21</v>
       </c>
     </row>

--- a/output/topology_excel/9945.xlsx
+++ b/output/topology_excel/9945.xlsx
@@ -462,10 +462,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -484,10 +484,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -506,10 +506,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -531,7 +531,7 @@
         <v>1</v>
       </c>
       <c r="B5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -553,7 +553,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -572,7 +572,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B7" t="n">
         <v>6</v>
@@ -594,7 +594,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B8" t="n">
         <v>7</v>
@@ -616,10 +616,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -652,10 +652,10 @@
         <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>245</v>
+        <v>479</v>
       </c>
       <c r="F10" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11">
@@ -663,7 +663,7 @@
         <v>1</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -674,10 +674,10 @@
         <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>161</v>
+        <v>100</v>
       </c>
       <c r="F11" t="n">
-        <v>11</v>
+        <v>71</v>
       </c>
     </row>
     <row r="12">
@@ -685,7 +685,7 @@
         <v>1</v>
       </c>
       <c r="B12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -696,10 +696,10 @@
         <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>479</v>
+        <v>173</v>
       </c>
       <c r="F12" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
@@ -718,10 +718,10 @@
         <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>314</v>
+        <v>245</v>
       </c>
       <c r="F13" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14">
@@ -729,7 +729,7 @@
         <v>2</v>
       </c>
       <c r="B14" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -740,10 +740,10 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>313</v>
+        <v>161</v>
       </c>
       <c r="F14" t="n">
-        <v>82</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15">
@@ -762,7 +762,7 @@
         <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>58</v>
+        <v>314</v>
       </c>
       <c r="F15" t="n">
         <v>13</v>
@@ -773,7 +773,7 @@
         <v>3</v>
       </c>
       <c r="B16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -784,10 +784,10 @@
         <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>206</v>
+        <v>313</v>
       </c>
       <c r="F16" t="n">
-        <v>18</v>
+        <v>82</v>
       </c>
     </row>
     <row r="17">
@@ -795,7 +795,7 @@
         <v>4</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -806,10 +806,10 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>156</v>
+        <v>58</v>
       </c>
       <c r="F17" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18">
@@ -817,7 +817,7 @@
         <v>4</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -828,18 +828,18 @@
         <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>100</v>
+        <v>206</v>
       </c>
       <c r="F18" t="n">
-        <v>71</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -850,7 +850,7 @@
         <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>120</v>
+        <v>154</v>
       </c>
       <c r="F19" t="n">
         <v>13</v>
@@ -858,10 +858,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>154</v>
+        <v>173</v>
       </c>
       <c r="F20" t="n">
         <v>13</v>
@@ -883,7 +883,7 @@
         <v>5</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -902,10 +902,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -916,18 +916,18 @@
         <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>173</v>
+        <v>151</v>
       </c>
       <c r="F22" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -938,18 +938,18 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>173</v>
+        <v>156</v>
       </c>
       <c r="F23" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B24" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -960,10 +960,10 @@
         <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>151</v>
+        <v>120</v>
       </c>
       <c r="F24" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/output/topology_excel/9945.xlsx
+++ b/output/topology_excel/9945.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,22 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Length</t>
+          <t>Length_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Width</t>
+          <t>Width_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Length_2</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Width_2</t>
         </is>
       </c>
     </row>
@@ -481,6 +491,8 @@
       <c r="F2" t="n">
         <v>13</v>
       </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -503,6 +515,8 @@
       <c r="F3" t="n">
         <v>13</v>
       </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -525,6 +539,8 @@
       <c r="F4" t="n">
         <v>11</v>
       </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -547,6 +563,8 @@
       <c r="F5" t="n">
         <v>13</v>
       </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -569,6 +587,8 @@
       <c r="F6" t="n">
         <v>15</v>
       </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -591,6 +611,8 @@
       <c r="F7" t="n">
         <v>13</v>
       </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -613,6 +635,8 @@
       <c r="F8" t="n">
         <v>13</v>
       </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -635,6 +659,8 @@
       <c r="F9" t="n">
         <v>13</v>
       </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -657,6 +683,8 @@
       <c r="F10" t="n">
         <v>13</v>
       </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -671,13 +699,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>100</v>
+        <v>58</v>
       </c>
       <c r="F11" t="n">
-        <v>71</v>
+        <v>11</v>
+      </c>
+      <c r="G11" t="n">
+        <v>89</v>
+      </c>
+      <c r="H11" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="12">
@@ -701,6 +735,8 @@
       <c r="F12" t="n">
         <v>8</v>
       </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -723,6 +759,8 @@
       <c r="F13" t="n">
         <v>11</v>
       </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -745,6 +783,8 @@
       <c r="F14" t="n">
         <v>11</v>
       </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -767,6 +807,8 @@
       <c r="F15" t="n">
         <v>13</v>
       </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -787,8 +829,10 @@
         <v>313</v>
       </c>
       <c r="F16" t="n">
-        <v>82</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -811,6 +855,8 @@
       <c r="F17" t="n">
         <v>13</v>
       </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -833,6 +879,8 @@
       <c r="F18" t="n">
         <v>18</v>
       </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -855,6 +903,8 @@
       <c r="F19" t="n">
         <v>13</v>
       </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -877,6 +927,8 @@
       <c r="F20" t="n">
         <v>13</v>
       </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -899,6 +951,8 @@
       <c r="F21" t="n">
         <v>15</v>
       </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -921,6 +975,8 @@
       <c r="F22" t="n">
         <v>21</v>
       </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -943,6 +999,8 @@
       <c r="F23" t="n">
         <v>21</v>
       </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -965,6 +1023,8 @@
       <c r="F24" t="n">
         <v>13</v>
       </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
